--- a/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
+++ b/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新谷コメント" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新谷コメント_完全版" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,14 +448,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="110" customWidth="1" min="5" max="5"/>
+    <col width="130" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,12 +475,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ご意見の要旨</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>新谷コメント（記入表の「新谷さんコメント入力用」列へ貼り付け）</t>
+          <t>新谷さんコメント入力用（この列を記入表へ貼り付け）</t>
         </is>
       </c>
     </row>
@@ -501,12 +495,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>STOメンバー選定基準／現任案件の遅延防止</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>採用します。ご指摘の通り、STO専任化は「現任業務の引き継ぎ計画」とセットでなければ現場に穴が空きます。人選の確定時には、①選定基準（現場からの信頼・データ・部門横断の調整力）と、②本人が現在担当している案件の移管先・移管スケジュールを必ずセットで提示し、経営会議で承認します。移管が成立しない場合は専任化の時期をずらします。計画遅延を出さないための最重要ポイントとして体制設計に組み込みます。</t>
+          <t>採用します。STO専任化は「現任業務の引き継ぎ計画」とセットでなければ現場に穴が空きます。その前提として、まず現在STO候補となるメンバーに依頼している業務・サポート中の案件が何かを正確に把握したいので、現状の依頼内容の一覧共有をお願いします。そのうえで人選確定時には、選定基準と担当案件の移管先・スケジュールを必ずセットで提示し承認します。移管が成立しなければ専任化の時期をずらします。</t>
         </is>
       </c>
     </row>
@@ -526,12 +515,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AI提案初稿後の商品企画イメージは誰が作るか</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>現時点の整理をお答えします。AIが担うのは「提案書の初稿」（構成・実績・文言・過去事例）までで、商品企画のクリエイティブイメージは当面「人」（現場＋デザインリソース）が担います。ここが現在の提案上のボトルネックという認識は同じです。だからこそ工数計測で企画イメージ作成の実工数を可視化し、デザイン組織の強化（No.20の永山さんのご提案と接続）やスタイルガイド資産のAI活用拡大を、データを根拠に判断します。90日のAI試験導入の範囲は提案書ドラフトまでに絞ります。</t>
+          <t>AIが担うのは提案書の初稿までで、企画クリエイティブは当面「人」が担います。ここがボトルネックという認識は同じです。そこで庄司さんにお願いがあります。①現状の提案書作成のワークフローを共有してください。②提案資料の「基本資料パック」（標準で使い回している共通資料）があれば共有してください。③もし案件ごとにオートクチュール（一点もの）で資料を作っているのであれば、その作成にかかっている時間の把握にご協力ください。この実態を踏まえて、デザインリソースの強化（No.20と接続）をデータを根拠に判断します。</t>
         </is>
       </c>
     </row>
@@ -551,12 +535,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>作品/メディアディストリビューションを改革の定義から切り離すべきでない</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>完全に同意です。IPの価値の源泉は作品であり、営業はその価値を毀損せず届け切る側です。評価軸に「IP/ブランド価値」を置いたのはまさにこの接続のためですが、ご指摘を受けて、改革の定義に「作品・メディアディストリビューションとの連動」を明記する修正を行います。作品・メディア側には監修改革WGとスコアリング基準の設計に参画いただきたく、改めてご相談します。</t>
+          <t>完全に同意です。改革の定義に「作品・メディアディストリビューションとの連動」を明記する修正を行います。監修改革WGとスコアリング基準設計への参画をご相談します。</t>
         </is>
       </c>
     </row>
@@ -576,12 +555,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>監修AI化による当事者意識低下の懸念／監修は提案機能でもある</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>重要なご指摘で、2点とも設計に反映します。①監修の定義を「品質保証＋より良くするための提案機能」として資料・WG設計要件に明記します（単なる間違い探しではない）。②AIの役割は「過去指摘の検索と一次チェック」に限定し、判断と提案は人が担う。さらにAIに蓄積されたナレッジを現場教育に使う「AIから学ぶ」設計をWGの要件に加えます。38度化させないというご指摘、まさに42度運営の核心だと受け止めました。優先順位付けは3トラック制の設計時に監修部門と共同で決めます。</t>
+          <t>2点とも設計に反映します。監修の定義を「品質保証＋提案機能」と明記し、AIは検索・一次チェックに限定して判断と提案は人が担います。AIナレッジを現場教育に使う「AIから学ぶ」設計をWG要件に加えます。38度化させないというご指摘は、42度運営の核心だと受け止めました。</t>
         </is>
       </c>
     </row>
@@ -601,12 +575,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>契約〜レベニューシェア特定まで採番制でE2E管理</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>採用します。案件IDの採番はマスタ設計に含めていますが、ご提案を受けて「契約・監修・ローンチ・レベニューシェア特定までを同一IDで一気通貫管理する」ことをプロセス改革WGの設計要件として明記します。担当者が替わっても業務の質が変わらない状態、ファイル探しに時間を取られない状態は、この改革の目指す姿そのものです。</t>
+          <t>採用します。契約・監修・ローンチ・レベニューシェア特定まで同一IDで一気通貫管理することを、プロセス改革WGの設計要件に明記します。</t>
         </is>
       </c>
     </row>
@@ -626,12 +595,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>「やめる」判断のIP特有の難しさ（数年戻れないリスク）</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>その通りで、これは「決め方の設計」の話だと私も考えます。だからこそ①撤退より省力化を優先する、②判断基準に「再参入可能性・ブランド成長段階」を織り込む、③やめる場合も「誠実な説明・代替提案・再開可能性の明示」をセットにした別れ方の標準を作る——の3点を設計に入れています。トリアージ基準の設計に、IP/エンタメ特有の観点を持つ橋本さんにぜひ参画いただきたいです。</t>
+          <t>「決め方の設計」の話という整理はその通りです。撤退より省力化を優先する／判断基準に再参入可能性を織り込む／別れ方の標準（誠実な説明・代替提案・再開可能性）をセットにする——の3点で設計します。トリアージ基準の設計に、ぜひ参画をお願いしたい。</t>
         </is>
       </c>
     </row>
@@ -651,12 +615,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>全社横断マーケティングカレンダーの整備</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>採用します。各部門バラバラのスプレッドシート管理が全社計画とグローバル対応の妨げになっているという認識は同じです。案件マスタ・ダッシュボードのデータ基盤要件に「全社マーケティングカレンダー」を追加し、標準化フェーズ（4〜6か月目）で単一基盤化します。第一歩として棚卸しの際に各部門の既存カレンダー・管理表も洗い出します。アクセス権はマネージャー以上とするご提案も含めて設計します。</t>
+          <t>採用します。データ基盤要件に追加し、標準化フェーズ（4〜6か月目）で単一基盤化します。棚卸しの際に各部門の既存カレンダー・管理表も洗い出します。</t>
         </is>
       </c>
     </row>
@@ -676,12 +635,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>標準プロセスにフォローアップ・プロモーションを追加／発売後の次提案は別案件か</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>採用します。獲得で終わらず相手のビジネスの成功に並走し続けるのが当社営業の特色というご指摘はその通りで、標準プロセスを「リード→商談→提案→条件合意→契約→監修→プロモーション→立ち上げ・運用→フォローアップ」に修正します。発売後フォロー・販売支援の工数も計測対象に含め、見えない貢献が評価されない状態をなくします。次の商品化提案は「別案件として起票」で認識合っています（同一顧客に紐づくので関係の継続性は顧客側で管理されます）。</t>
+          <t>採用します。獲得で終わらず相手のビジネスの成功に並走し続けるのが当社営業の特色というご指摘はその通りで、標準プロセスを「リード→商談→提案→条件合意→契約→監修→プロモーション→立ち上げ・運用→フォローアップ」に修正します。発売後フォロー・販売支援の工数も計測対象に含め、見えない貢献が評価されない状態をなくします。次の商品化提案は「別案件として起票」で認識合っています（同一顧客に紐づくので、関係の継続性は顧客側で管理されます）。</t>
         </is>
       </c>
     </row>
@@ -701,12 +655,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>（本文の記載が途中の様子）</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>商品化ライセンス＋広告共通という前提は承知しました。こちらの行はご意見の本文が未記載のようです。追記いただくか、口頭でも結構ですので直接お聞かせください。なお棚卸し・スコアリングは商品化と広告を共通の仕組みで設計します（領域選択肢に「商品化＋広告共通」を追加します）。</t>
+          <t>重要な指摘で、2点とも対応します。①分単位の正確な記憶は求めません。0.5時間単位・記憶ベース・精度7割で十分という設計です（正確さより続くことを優先）。そのうえで、音声メモを入れると要約・分類して記録化してくれるAI支援は、まさに構想している「商談記録の自動化」ユースケースそのものなので、AI試験導入の候補に正式に加えます。トライアル希望の営業管理ツールの件も含めて検討します。②活動工程の10分類は全社共通の「粗い物差し」として設計していますが、部門特有の工程があるのはその通りなので、領域ごとの追加項目を認める設計にします。連携窓口役を通じて各部門の実情に合わせて調整しましょう。</t>
         </is>
       </c>
     </row>
@@ -726,11 +675,6 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ライブ案件は単年度収益でなく総合評価を／品質維持工数は投資として扱うべき</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
           <t>同意します。7つの評価軸（CRM価値・ブランド価値・海外展開価値・戦略価値）は、まさにライブのような「単年度売上に表れない価値」を正当に評価するために設計しています。継続開催によるLTVの観点は顧客ランクとスコア運用に反映します。工数についても重要なご指摘で、工数分類に「品質維持・ブランド価値向上のための投資工数」（スーツメンテ・キャスト育成等）の区分を設け、削減対象と混ざらないようにします。工数計測は削るためだけでなく「必要な投資を証明するため」にも使ってください。</t>
         </is>
       </c>
@@ -751,12 +695,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>全社員への理解浸透／属人化業務の徹底的な顕在化</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>同意します。浸透のために、メンバー向け説明会資料（15分＋想定問答）を全領域で実施し、決定事項は台帳で全員に見える形にします。属人化の顕在化はまさに第1段階の棚卸しの目的です。「あの人しか知らない」を責めるのではなく、組織の資産に変換する趣旨で進めますので、流通営業部での説明会にはぜひ田代さんにも同席いただきたいです。</t>
+          <t>同意します。浸透のために、メンバー向け説明会（15分＋想定問答）を全領域で実施し、決定事項は台帳で全員に見える形にします。属人化の顕在化はまさに第1段階の棚卸しの目的です。「あの人しか知らない」を責めるのではなく、組織の資産に変換する趣旨で進めますので、流通営業部での説明会にはぜひ田代さんにも同席いただきたいです。</t>
         </is>
       </c>
     </row>
@@ -776,12 +715,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>売上規模より中長期のブランドバリュー寄与を最重要の判断軸に</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>同意します。この思想はスコアリング設計に既に織り込んでおり、ブランド毀損リスクのある案件は点数に関わらずエスカレーションする設計です。ウェイト（どの観点を重くするか）を決める経営検討会で、「ブランドバリュー寄与を最重要とする」というご意見を正式に議題にします。パートナー選定基準にも同じ思想を反映します。</t>
+          <t>同意します。毀損リスク案件は点数に関わらずエスカレーションする設計とし、ウェイトを決める経営検討会でこのご意見を正式議題にします。加えて、この機会にやりたいのは「ブランド毀損とは何か」の形式知化です。毀損にあたる条件は何か、ウルトラマンのイメージに合うパートナー・プロジェクトとはどういうものか——これまで暗黙知で判断されてきた基準を明文化し、誰が見ても同じ判断ができる状態にします。この基準づくりに田代さんの知見をぜひお借りしたい。</t>
         </is>
       </c>
     </row>
@@ -801,12 +735,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>トップ外交と現場の乖離防止（負荷・コスト・モチベーション）</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>同意します。トップ外交の仕組みは「経営が種を持ってきて現場に丸投げする」形になったら失敗です。設計上、記録・追跡は事務局が巻き取り、案件化の判断時には担当部門の工数・実現性・収益性を確認するステップを入れます。先方企業との間でも、トップ間の話と実務の話が乖離しないよう、面談メモを実務担当に必ず共有する運用にします。乖離を感じたら月次会議で遠慮なく指摘してください。</t>
+          <t>同意します。そして率直に言えば、これまでトップ外交は十分に成果につながっていません。だからこそ、登録→アサイン→30日以内初動という仕組みに変えます。記録・追跡は事務局が巻き取り、案件化の判断時には担当部門の工数・実現性を確認するステップを入れ、現場への丸投げを構造的に防ぎます。乖離を感じたら月次会議で遠慮なく指摘してください。</t>
         </is>
       </c>
     </row>
@@ -826,12 +755,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>（本文の記載が途中の様子）</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>No.9と同様、本文が未記載のようです。売上偏重の評価軸に関するご意見をお持ちでしたら、ぜひ追記または直接お聞かせください。商品化＋広告共通の評価軸設計には成岡さんの現場知見を反映したいと考えています。</t>
+          <t>趣旨、受け取りました。売上・粗利だけでなく、ブランド価値の向上とファンベースの拡大を評価軸に据えるべき——まさにその思想で7軸（ブランド価値・CRM価値＝ファンとのつながり）を設計しています。商品化＋広告領域では特に「ファンベース拡大への寄与」をどう測るかが論点になるので、ウェイトを決める経営検討会の前に、成岡さんの考える測り方（例：新規ファン接点数、ターゲット層の広がり等）をぜひ聞かせてください。文面が途中のようでしたら、続きは口頭でも結構です。</t>
         </is>
       </c>
     </row>
@@ -851,12 +775,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>システム乱立・共有フォルダの煩雑さ。AI活用の前に要不要の整理を</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>採用します。おっしゃる通り、散らかった基盤の上にAIを乗せても機能しません。第1段階の棚卸しに「社内システム・データ保存先の棚卸し」を追加し、6か月目のシステム投資判断の前提材料にします。ただしAI試験導入（提案書初稿・監修ナレッジ検索の2つ）は範囲が限定的で既存システムへの依存が小さいため、整理と並行で進めます。</t>
+          <t>採用します。第1段階に「社内システム・保存先の棚卸し」を追加し、6か月目のシステム投資判断の前提にします。AI試験導入2件は既存システムへの依存が小さいため、整理と並行で進めます。</t>
         </is>
       </c>
     </row>
@@ -876,12 +795,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>管理強化にならない運用／ネガティブ情報を隠さず報告できる文化</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>最重要のご指摘です。仕組みとしては①工数データは評価に使わない宣言、②停滞表示は「誰が悪いか」ではなく「誰が助けるか」のシグナル、③明細は本人と事務局のみ閲覧——を用意しましたが、文化は仕組みだけでは作れません。最初に悪い報告が上がってきたとき、経営が責めずに「言ってくれてありがとう」から入れるか。ここは私自身の行動で示します。もし運用が約束から外れたら、直接私に指摘してください。</t>
+          <t>最重要のご指摘です。仕組み（評価に使わない宣言・停滞は支援のシグナル・明細は本人と事務局のみ）は用意しましたが、文化は仕組みだけでは作れません。最初に悪い報告が上がってきたとき、経営が責めずに「言ってくれてありがとう」から入れるか。ここは私自身の行動で示します。</t>
         </is>
       </c>
     </row>
@@ -901,12 +815,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>現場の良心に基づく仕事の存在／1社員まで届く粒度の周知</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>同意します。「誰かに迷惑がかかるから」と現場の良心で続いている仕事は、やめる判断を会社が明示しない限り消えません。だからやらない判断は経営の名前で出し、決定台帳で全員が見られるようにします。周知は説明会・FAQ・部長からの部内展開の3経路で行いますが、「1社員まで届く粒度」のご指摘を受け、決定事項の社内向けかみ砕き版（1決定1段落）を事務局から毎月出す運用を加えます。</t>
+          <t>同意します。やらない判断は経営の名前で出し、決定台帳で見える化します。ご指摘を受け、「決定事項のかみ砕き版（1決定1段落）」を事務局から毎月出す運用を加えます。ただし、これを1社員まで届け切る最後の区間は、部長の皆さんの部内展開なしには実現できません。かみ砕き版は事務局が用意しますので、部内へ届ける役はぜひお願いします。</t>
         </is>
       </c>
     </row>
@@ -926,12 +835,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>各部署が動けるよう設計しスケジュールを振り出すリード部署が必要</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>その機能を担うのが専任の推進チーム（事務局・PMO）です。役割として①棚卸しなど実務の下書き・巻き取り、②各部門のタスクとスケジュールの振り出し・進捗管理、③会議アジェンダの設計を明確に持たせます。加えて各部門に連携窓口役を置き、部門側の受け口も明確にします。「設計しなおし」が必要な業務フローが商品開発部にあれば、初期ヒアリングでぜひ聞かせてください。</t>
+          <t>その機能を担うのが専任推進チーム（事務局）です。各部門のタスクとスケジュールの振り出し・進捗管理を役割として明確に持たせ、各部門には連携窓口役を置いて受け口も明確にします。</t>
         </is>
       </c>
     </row>
@@ -951,12 +855,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>自社MD・流通の見える化／売上・利益・在庫の週次確認と担当者レベルの週次レビュー</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>採用します。自社MDは改革対象の12領域に含まれており、売上・利益・在庫を週次で見られる仕組みは第2段階のダッシュボード設計で優先度高く扱います。「自分たちの給料はどこから捻出されているのかを自分ごとに」という視点は、まさにこの改革の思想（全員が営業マインドを持つ）と同じです。担当者レベルの週次レビューは、新設する週次会議の枠組みの中で自社MD領域から先行導入しましょう。</t>
+          <t>採用します。売上・利益・在庫の週次ダッシュボードは第2段階で優先度高く設計し、担当者レベルの週次レビューは自社MD領域から先行導入しましょう。</t>
         </is>
       </c>
     </row>
@@ -976,12 +875,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>社内デザイン組織の強化／アート・二次創作デザイン資産の管理・蓄積（SCLA参考）</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>重要な提案として持ち帰ります。営業改革の直接の範囲は超えますが、①提案書に付随する企画イメージ作成のリソース問題（No.2）、②スタイルガイド資産のナレッジDB化はこの改革のデータ基盤と直結します。デザイン資産の蓄積・管理は「経営基盤強化」の検討テーマとして正式に起票し、SCLAの考え方も含めて検討します。具体的なイメージを一度聞かせてください。</t>
+          <t>重要な提案として持ち帰ります。営業改革の直接範囲は超えますが、No.2の課題（提案書の企画イメージ作成）とナレッジ基盤に直結するため、「経営基盤強化」の検討テーマとして正式に起票します。</t>
         </is>
       </c>
     </row>
@@ -1001,12 +895,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>経営陣全員のコミットとコア人員のリソース確保／推進側と現業を守る側の明確化</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>完全に同意します。経営のコミットは、月次会議への出席・撤退判断の実行・トップ外交の48時間登録という「行動」で担保し、逃げ道を作りません。人員減の中での改革というご指摘は重く受け止めており、コアメンバーは専任化＋現業の移管計画をセットで承認（No.1と同方針）、「推進する担当」と「現状業務を守る担当」の分離を体制設計に採用します。リソース計画は高橋さんと一緒に詰めさせてください。</t>
+          <t>完全に同意します。経営のコミットは、月次会議への出席・撤退判断の実行・トップ外交の48時間登録という「行動」で担保します。コア人員は専任化＋現業の移管計画をセットで承認し、「推進する担当」と「現状業務を守る担当」の分離を体制設計に採用します。リソース計画は高橋さんと一緒に詰めさせてください。そして申し上げたいのは——部長の皆さんこそが経営陣の一員だということです。この改革は、皆さんと一緒に経営として進めます。</t>
         </is>
       </c>
     </row>
@@ -1026,12 +915,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>契約まわりの改革はすぐ動ける。HD側の新規人員を最優先で稼働可能</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>大変ありがたいお申し出です。契約改革（雛形整備・条件の標準メニュー化・過去契約の検索可能化・採番制）はWGを先行して立ち上げます。HD側人材のアサインについて、今週中に個別にご相談させてください。監修・法務と併せて、リードタイム実測から着手します。</t>
+          <t>大変ありがたいお申し出です。契約改革WG（雛形整備・条件標準メニュー・過去契約の検索可能化・採番制）を先行して立ち上げます。HD側人材のアサインについて、今週中に個別にご相談させてください。</t>
         </is>
       </c>
     </row>

--- a/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
+++ b/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -919,6 +919,266 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>販売促進部</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>井上</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>深く受け止めました。組織変更後の疲弊があるなかでの改革だという現実認識は、私も同じです。だからこそ約束します。①経営が最も汗をかく——月次会議への出席、撤退判断の責任、48時間ルールという「行動」で示します。②負荷の順序を守る——現場への「お願い」より先に、資料作成の廃止・下書きの巻き取りなど「楽になること」を先に届けます。③処遇への反映——安易な約束はしませんが、改革の成果が出た先に、それが処遇に反映される会社にしていく意思は明確に持っています（評価制度との接続は改革後半で正式に設計します）。継続発信については、毎月の「決定事項のかみ砕き版」に加え、節目ごとに私から全社へ直接メッセージを出します。部長の皆さんの日々の声掛けと、両輪でやらせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>販売促進部</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>井上</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>採用します。AIが担うのは提案書の初稿までで、クリエイティブが必要な場面ではデザイナーの支援が不可欠——庄司さん（No.2）・永山さん（No.20）と同根のご指摘です。まず工数計測で、販売促進部への依頼の実態（件数・工数・繁閑）を見える化し、それを根拠に販促部のリソース強化・体制整備を改革スコープの検討対象に正式に含めます。「受けきれない状態を個人の頑張りで吸収する」ことはさせません。全面協力のお申し出、心強いです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>商品開発部</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>山田</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>重要な指摘です。会長直下案件の情報が個人に紐づき、組織の取り組みにならない——まさにこの構造を変えるのが「トップ外交管理」の仕組みです。面談・案件の48時間以内登録→担当アサイン→30日以内初動→進捗の見える化を、会長案件も例外なく適用します（ここが肝だと考えています）。会長ご自身が出席する点検会議で進捗を確認する構造にすることで、「個人の案件」から「組織の案件」に変えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>商品開発部</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>山田</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>同意します。スピードを優先するあまり品質・安心安全が犠牲になれば、ブランドにとって最大の損失になる——42度の設計思想（45度は疲弊し、事故を生む）はまさにこの点です。対応として、①工数の見える化で「一部への急激な負荷集中」を検知し、会議で再配分を決める、②「やり切る」の定義に品質・安全の基準を含める（不十分な状態で世に出すことは『やり切った』とみなさない）、の2点を運営ルールに反映します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>商品開発部</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>山田</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>完全に同意します。「できたものは、その時点で過去のもの」——この言葉は、この改革の思想そのものです。仕組み側も同じ原則で運営します：90日ごとに仕組み自体を見直し、形骸化したものは廃止・変更する。前年踏襲を疑うマインドは、説明会・決定事項の共有・成功事例の横展開を通じて浸透させますが、山田さんのこの言葉をぜひ全社に紹介させてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>製作企画部</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>石塚</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>採用します。作品・企画情報が営業現場まで届かず「啓蒙的」な個別説明が発生している——この双方のロスは、橋本さん指摘の「作品との連動」（No.3）の最も具体的な改善テーマです。対応として、①全社マーケティングカレンダー（No.7で採用済み）に製作企画のタイムライン（TVシリーズ・27年ゼロ映画等）を統合、②案件一覧の基盤に「作品・企画情報」のビューを追加し、営業が自発的に情報を取れる形に、③標準プロセスの上流に「企画段階からの営業・製作対話」のステップを設計——を進めます。製作企画部にもこの設計に参画いただきたい。ぜひ一緒に作りましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>製作企画部</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>石塚</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>重要なテーマとして受け取りました。IP開発への投資判断は営業改革の直接範囲を超えますが、「作品単体の収支シミュレーションを基盤に、ブランド軸・グループ貢献軸を含めた判断基準を作る」という方向は、案件の7軸評価と完全に同じ思想です。投資開発判断基準の共同設計に賛成します。HDとの原資・成長投資枠の議論は経営アジェンダとして正式に起票します。まず現状の作品単体収支シミュレーションの仕組みを教えてください。そこを出発点にしましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>カード開発部</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>宍戸</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>スコープの認識、合っています（商品開発本部・カード開発部も対象です）。そして「行動設計＋予算＋評価の三点セット」というご指摘は本質です。そのうえで順序の設計意図をお伝えします。予算との連携は、6か月目のシステム投資判断と来期予算へのKPI組み込みで対応します。評価制度との連携は、意図的に改革後半（10〜12か月目）に置いています——初年度前半に評価と結びつけると「工数記録＝査定」という誤解が生まれ、データが歪むためです。横連携を促す評価設計は定着化フェーズで必ず扱いますので、その際は宍戸さんの知見をお借りしたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>カード開発部</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>宍戸</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>素晴らしい提案です。カードアプリのユーザーデータは、全社顧客台帳の先行モデルになり得ます。「データ取得や分析が目的ではなく、課題発見・仮説検証のためにデータと施策をセットで」という姿勢も、この改革の思想と完全に一致します。ご提案の領域別の北極星指標・先行指標（売上/収録カード数、カード何種開発、ユーザーの獲得・維持・復帰・成長など）は、KPIの領域別展開の第1号としてカード領域から着手しましょう。データポータルの共有ありがとうございます。拝見のうえ、個別に設計の時間を取らせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>新規開拓</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>成岡</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>こちらの行はご意見の本文が未記載のようです。ライセンス領域の「懸念・やれない事情」とのことなので、重要な論点の可能性があります。追記いただくか、口頭でも結構ですので直接お聞かせください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>HDグループ事業経営戦略本部</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>木綿</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>同意します。「どんなブランドと組んでいきたいか」は、進行中の「ブランド毀損基準の形式知化」（No.12）の裏面です。毀損条件のネガティブリストだけでなく、「目指す協業像・組みたい相手」のポジティブリストもセットで明文化します。PR・ブランディング・クリエイティブ開発との連携強化は、案件評価のIP適合軸の運用に組み込みます。この基準づくりに、HD側の視点でぜひ参画してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HDグループ事業経営戦略本部</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>木綿</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>面白いご提案です。そして内覧会でいただいたストリート系ファッションブランドからの声は、まさに「接点から生まれた商談の種」です。仕組みの実践第1号として、さっそく案件登録→担当アサイン→30日以内の初動につなげましょう（詳細を教えてください）。ウルトラマートの営業拠点としての活用は、接点づくりの検討テーマとして正式に起票します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>HDグループ事業経営戦略本部</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>木綿</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>文面が途中のようです。「新しい顧客層を取りに行くために」——自社MDの顧客層拡大は重要テーマなので、続きをぜひ聞かせてください（追記でも口頭でも結構です）。No.34のファッションブランドの件とつながる話であれば、あわせて伺います。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
+++ b/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>趣旨、受け取りました。売上・粗利だけでなく、ブランド価値の向上とファンベースの拡大を評価軸に据えるべき——まさにその思想で7軸（ブランド価値・CRM価値＝ファンとのつながり）を設計しています。商品化＋広告領域では特に「ファンベース拡大への寄与」をどう測るかが論点になるので、ウェイトを決める経営検討会の前に、成岡さんの考える測り方（例：新規ファン接点数、ターゲット層の広がり等）をぜひ聞かせてください。文面が途中のようでしたら、続きは口頭でも結構です。</t>
+          <t>採用します。ファンベース拡大への取組と「未開拓地域への協力」を取引先評価に加える——顧客ランクの「海外価値」軸は『未開拓市場の扉を開ける力』を評価する設計にしており、国内の未開拓地域・チャネルへの貢献も同じ思想で織り込みます。そして「定性的な項目には基準がほしい」はその通りです。すでに5段階の点数それぞれに『具体的な状態』を紐づけた採点定義（誰が採点しても同じ点になるアンカー方式）を作成済みで、近日展開します。『こんなすごいところとやれる』という実績が持つシグナル効果（ブランドの格を上げる協業）も、ブランド軸の採点定義に含めます。測り方の細部は、ウェイトを決める経営検討会の前に成岡さんの知見を聞かせてください。</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>こちらの行はご意見の本文が未記載のようです。ライセンス領域の「懸念・やれない事情」とのことなので、重要な論点の可能性があります。追記いただくか、口頭でも結構ですので直接お聞かせください。</t>
+          <t>極めて重要な指摘で、全面的に採用します。見える化の目的は「経営が全部を握る」ことではなく、その逆——現場で決め切れる範囲を広げることです。運営原則も『現場で決められることは現場で決め切る。上の会議にはそこでしか決められないことだけを上げる』としています。そのうえでご提案の通り、判断権限の3階層基準（①経営判断レベル／②部門長判断レベル／③現場担当者が自走できるレベル）を明文化します——決裁基準表として標準プロセスに組み込み、経営基盤強化の検討テーマに正式追加します。物差し（スコアと基準）があるほど、担当者は経営に聞かずに自分で判断できるようになる。見える化は自走を広げる道具にします。</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,47 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>文面が途中のようです。「新しい顧客層を取りに行くために」——自社MDの顧客層拡大は重要テーマなので、続きをぜひ聞かせてください（追記でも口頭でも結構です）。No.34のファッションブランドの件とつながる話であれば、あわせて伺います。</t>
+          <t>同意します。新しい顧客層を取りに行くには、デザイン・世界観・PR/SNSの一貫性が生命線というご指摘はその通りです。クリエイティブ組織の強化は永山さん（No.20）・井上さん（No.24）と同根のテーマとして「経営基盤強化」に正式起票済みで、木綿さんのご意見もそこに束ねます。加えて「リサーチ強化」（グループインタビュー・ターゲット理解・商品開発のアイデア出し）は新しい論点で、消費者・ファン理解＝接点づくりの検討テーマに組み込みます。HD側の視点で、ぜひ設計に参画してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>HDグループ事業経営戦略本部</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>木綿</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>同意します。企画・キャンペーン設計・クリエイティブを自ら仕掛けられる組織になる——まさに営業を『許諾の受け窓口』から『企画を仕掛ける側』へ変えるという、この改革の目指す姿です。AIが提案書の初稿を作り、人が企画とクリエイティブに時間を使う分担もそのための設計です。企画・クリエイティブ体制の強化は、庄司さん（No.2）・永山さん（No.20）・井上さん（No.24）・No.35と束ねて一つの検討テーマとして扱います。『面白い話題になる取り組み』の第1号として、No.34のファッションブランドの件をぜひ形にしましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ライブイベント部</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>菅野</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>重要な論点をありがとうございます。各部門の営業拡大に伴い、キャラクター稼働・連動企画の依頼がライブイベント部に集中し、担当者からの申請ベースで受け続けている——この「社内依頼の受け口が疲弊する」構造は、まさに見える化とトリアージの対象です。対応を2つ約束します。①部門横断の依頼（キャラクター稼働・連動企画）も『案件』として登録し、工数と優先順位が全社で見える状態にします。依頼側の熱量ではなく、全社共通の物差しで優先順位を決められるようにします。②申請→承認フローの整理を、判断基準（スコア）と決裁権限の階層（No.32の3階層基準）とセットでプロセス改革の検討項目に正式追加します。各部門の上長間での優先順位確認は、月例の案件会議がその場になります。フロー設計には菅野さんにぜひ参画いただきたい。</t>
         </is>
       </c>
     </row>

--- a/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
+++ b/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>完全に同意です。改革の定義に「作品・メディアディストリビューションとの連動」を明記する修正を行います。監修改革WGとスコアリング基準設計への参画をご相談します。</t>
+          <t>同意します。改革の定義に「作品・メディアディストリビューションとの連動」を明記する修正を行います。監修改革WGとスコアリング基準の設計に、TFEIからの参画をご相談します。</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2点とも設計に反映します。監修の定義を「品質保証＋提案機能」と明記し、AIは検索・一次チェックに限定して判断と提案は人が担います。AIナレッジを現場教育に使う「AIから学ぶ」設計をWG要件に加えます。38度化させないというご指摘は、42度運営の核心だと受け止めました。</t>
+          <t>2点とも設計に反映します。監修の定義は「品質保証＋提案機能」と明記し、AIは過去指摘の検索と一次チェックまで、判断と提案は人が担う分担にします。AIに蓄積したナレッジを現場教育に使う仕組みもWGの要件に加えます。監修の優先順位付けは3トラック制の設計時に監修部門と決めます。</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>同意します。そして率直に言えば、これまでトップ外交は十分に成果につながっていません。だからこそ、登録→アサイン→30日以内初動という仕組みに変えます。記録・追跡は事務局が巻き取り、案件化の判断時には担当部門の工数・実現性を確認するステップを入れ、現場への丸投げを構造的に防ぎます。乖離を感じたら月次会議で遠慮なく指摘してください。</t>
+          <t>同意します。これまでトップ外交が成果につながってこなかったのは事実なので、登録→アサイン→30日以内初動のルールに変えます。記録・追跡は事務局が持ち、案件化の判断時には担当部門の工数・実現性を確認するステップを入れます。現場との乖離を感じたら月次会議で指摘してください。</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>最重要のご指摘です。仕組み（評価に使わない宣言・停滞は支援のシグナル・明細は本人と事務局のみ）は用意しましたが、文化は仕組みだけでは作れません。最初に悪い報告が上がってきたとき、経営が責めずに「言ってくれてありがとう」から入れるか。ここは私自身の行動で示します。</t>
+          <t>その通りだと思います。仕組みとしては、評価に使わない・停滞表示は支援のシグナル・明細は本人と事務局のみ、を徹底します。実際に運用が始まったら、ネガティブな報告が不利に扱われていないか、永山さんの目でも見ていてください。おかしければ直します。</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>完全に同意します。経営のコミットは、月次会議への出席・撤退判断の実行・トップ外交の48時間登録という「行動」で担保します。コア人員は専任化＋現業の移管計画をセットで承認し、「推進する担当」と「現状業務を守る担当」の分離を体制設計に採用します。リソース計画は高橋さんと一緒に詰めさせてください。そして申し上げたいのは——部長の皆さんこそが経営陣の一員だということです。この改革は、皆さんと一緒に経営として進めます。</t>
+          <t>同意します。経営のコミットは、月次会議への出席・撤退判断・48時間ルールの実行で担保します。コア人員は専任化と現業の移管計画をセットで確定し、「推進する担当」と「現状業務を守る担当」は分けます。人員が減っている中での改革だという前提は体制設計に織り込みますので、リソース計画は高橋さんと詰めさせてください。</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>深く受け止めました。組織変更後の疲弊があるなかでの改革だという現実認識は、私も同じです。だからこそ約束します。①経営が最も汗をかく——月次会議への出席、撤退判断の責任、48時間ルールという「行動」で示します。②負荷の順序を守る——現場への「お願い」より先に、資料作成の廃止・下書きの巻き取りなど「楽になること」を先に届けます。③処遇への反映——安易な約束はしませんが、改革の成果が出た先に、それが処遇に反映される会社にしていく意思は明確に持っています（評価制度との接続は改革後半で正式に設計します）。継続発信については、毎月の「決定事項のかみ砕き版」に加え、節目ごとに私から全社へ直接メッセージを出します。部長の皆さんの日々の声掛けと、両輪でやらせてください。</t>
+          <t>現場が疲弊しているという認識は私も同じです。そのうえで、進め方は次の通りにします。①現場へのお願いより先に、資料作成の廃止・リスト下書きの巻き取りなど、負荷が減るものから着手する。②処遇への反映は、現時点で安易に約束はしません。評価制度との接続は改革後半で正式に設計し、その時点で方針を示します。③全社への発信は、毎月の決定事項の共有と節目ごとのメッセージで続けます。部長の皆さんの日々の声掛けと併せてお願いします。</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>採用します。AIが担うのは提案書の初稿までで、クリエイティブが必要な場面ではデザイナーの支援が不可欠——庄司さん（No.2）・永山さん（No.20）と同根のご指摘です。まず工数計測で、販売促進部への依頼の実態（件数・工数・繁閑）を見える化し、それを根拠に販促部のリソース強化・体制整備を改革スコープの検討対象に正式に含めます。「受けきれない状態を個人の頑張りで吸収する」ことはさせません。全面協力のお申し出、心強いです。</t>
+          <t>採用します。AIが担うのは提案書の初稿までで、クリエイティブ制作はデザイナーの支援が必要——庄司さん（No.2）・永山さん（No.20）と同根の論点です。まず工数計測で販売促進部への依頼の実態（件数・工数・繁閑）を把握し、それを根拠に販促部のリソース強化・体制整備を検討スコープに含めます。実態把握の際はご協力ください。</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>重要な指摘です。会長直下案件の情報が個人に紐づき、組織の取り組みにならない——まさにこの構造を変えるのが「トップ外交管理」の仕組みです。面談・案件の48時間以内登録→担当アサイン→30日以内初動→進捗の見える化を、会長案件も例外なく適用します（ここが肝だと考えています）。会長ご自身が出席する点検会議で進捗を確認する構造にすることで、「個人の案件」から「組織の案件」に変えます。</t>
+          <t>重要な指摘です。会長直下の案件も含めて、面談・案件は48時間以内の登録→担当アサイン→30日以内初動のルールに乗せます。例外は作りません。会長が出席する点検会議で進捗を確認する運用にすることで、個人に紐づいた情報が組織で共有される状態にします。</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>同意します。スピードを優先するあまり品質・安心安全が犠牲になれば、ブランドにとって最大の損失になる——42度の設計思想（45度は疲弊し、事故を生む）はまさにこの点です。対応として、①工数の見える化で「一部への急激な負荷集中」を検知し、会議で再配分を決める、②「やり切る」の定義に品質・安全の基準を含める（不十分な状態で世に出すことは『やり切った』とみなさない）、の2点を運営ルールに反映します。</t>
+          <t>同意します。負荷が一部に集中していないかは工数データで確認し、会議で再配分を判断します。また、品質・安全が不十分な状態で世に出すことは成果とみなさない前提で運営します。スピードと品質のバランスが崩れていると感じたら、その時点で指摘してください。</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>完全に同意します。「できたものは、その時点で過去のもの」——この言葉は、この改革の思想そのものです。仕組み側も同じ原則で運営します：90日ごとに仕組み自体を見直し、形骸化したものは廃止・変更する。前年踏襲を疑うマインドは、説明会・決定事項の共有・成功事例の横展開を通じて浸透させますが、山田さんのこの言葉をぜひ全社に紹介させてください。</t>
+          <t>同意します。仕組みの側も同じ考え方で運営します。90日ごとに仕組み自体を見直し、機能していないものは廃止・変更します。運用が前例踏襲になっていると気づいたら、都度指摘してください。</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>採用します。作品・企画情報が営業現場まで届かず「啓蒙的」な個別説明が発生している——この双方のロスは、橋本さん指摘の「作品との連動」（No.3）の最も具体的な改善テーマです。対応として、①全社マーケティングカレンダー（No.7で採用済み）に製作企画のタイムライン（TVシリーズ・27年ゼロ映画等）を統合、②案件一覧の基盤に「作品・企画情報」のビューを追加し、営業が自発的に情報を取れる形に、③標準プロセスの上流に「企画段階からの営業・製作対話」のステップを設計——を進めます。製作企画部にもこの設計に参画いただきたい。ぜひ一緒に作りましょう。</t>
+          <t>採用します。作品・企画情報が営業現場まで届かず、個別説明の手間が双方に発生しているのはロスです。対応として、①全社マーケティングカレンダー（No.7で採用済み）に製作企画のタイムラインを統合、②案件一覧の基盤に作品・企画情報のビューを追加、③標準プロセスの上流に企画段階からの営業・製作の対話ステップを設計——を進めます。この設計に製作企画部の参画をお願いします。</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>素晴らしい提案です。カードアプリのユーザーデータは、全社顧客台帳の先行モデルになり得ます。「データ取得や分析が目的ではなく、課題発見・仮説検証のためにデータと施策をセットで」という姿勢も、この改革の思想と完全に一致します。ご提案の領域別の北極星指標・先行指標（売上/収録カード数、カード何種開発、ユーザーの獲得・維持・復帰・成長など）は、KPIの領域別展開の第1号としてカード領域から着手しましょう。データポータルの共有ありがとうございます。拝見のうえ、個別に設計の時間を取らせてください。</t>
+          <t>賛成です。カードアプリのユーザーデータは、全社の顧客データ基盤の先行事例になります。データは分析が目的ではなく課題発見・仮説検証のため、という前提も同じ認識です。領域別のKPI設計（売上/収録カード数、ユーザーの獲得・維持・復帰・成長など）はカード領域から着手しましょう。データポータルを拝見したうえで、設計の時間をください。</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>極めて重要な指摘で、全面的に採用します。見える化の目的は「経営が全部を握る」ことではなく、その逆——現場で決め切れる範囲を広げることです。運営原則も『現場で決められることは現場で決め切る。上の会議にはそこでしか決められないことだけを上げる』としています。そのうえでご提案の通り、判断権限の3階層基準（①経営判断レベル／②部門長判断レベル／③現場担当者が自走できるレベル）を明文化します——決裁基準表として標準プロセスに組み込み、経営基盤強化の検討テーマに正式追加します。物差し（スコアと基準）があるほど、担当者は経営に聞かずに自分で判断できるようになる。見える化は自走を広げる道具にします。</t>
+          <t>重要な指摘で、採用します。見える化の目的は経営が全部を握ることではなく、現場で決め切れる範囲を広げることです。運営原則も「現場で決められることは現場で決め切る。上の会議にはそこでしか決められないことだけを上げる」としています。ご提案の判断権限の3階層基準（経営判断／部門長判断／担当者が自走できる範囲）は明文化し、決裁基準表として標準プロセスに組み込みます。経営基盤強化の検討テーマに追加します。</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>同意します。企画・キャンペーン設計・クリエイティブを自ら仕掛けられる組織になる——まさに営業を『許諾の受け窓口』から『企画を仕掛ける側』へ変えるという、この改革の目指す姿です。AIが提案書の初稿を作り、人が企画とクリエイティブに時間を使う分担もそのための設計です。企画・クリエイティブ体制の強化は、庄司さん（No.2）・永山さん（No.20）・井上さん（No.24）・No.35と束ねて一つの検討テーマとして扱います。『面白い話題になる取り組み』の第1号として、No.34のファッションブランドの件をぜひ形にしましょう。</t>
+          <t>同意します。企画・キャンペーン設計・クリエイティブを自分たちから仕掛けられる体制は、営業を許諾の受け窓口で終わらせないために必要です。この論点は庄司さん（No.2）・永山さん（No.20）・井上さん（No.24）・No.35と束ねて、企画・クリエイティブ体制の強化として一つの検討テーマで扱います。第1号案件として、No.34のファッションブランドの件を具体化しましょう。</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>重要な論点をありがとうございます。各部門の営業拡大に伴い、キャラクター稼働・連動企画の依頼がライブイベント部に集中し、担当者からの申請ベースで受け続けている——この「社内依頼の受け口が疲弊する」構造は、まさに見える化とトリアージの対象です。対応を2つ約束します。①部門横断の依頼（キャラクター稼働・連動企画）も『案件』として登録し、工数と優先順位が全社で見える状態にします。依頼側の熱量ではなく、全社共通の物差しで優先順位を決められるようにします。②申請→承認フローの整理を、判断基準（スコア）と決裁権限の階層（No.32の3階層基準）とセットでプロセス改革の検討項目に正式追加します。各部門の上長間での優先順位確認は、月例の案件会議がその場になります。フロー設計には菅野さんにぜひ参画いただきたい。</t>
+          <t>重要な論点です。キャラクター稼働・連動企画の依頼がライブイベント部に集中し、申請ベースで受け続けている構造は、見える化と優先順位づけの対象そのものです。対応は2つ。①部門横断の依頼も「案件」として登録し、工数と優先順位が全社で見える状態にする——依頼側の熱量ではなく共通の物差しで判断できるようにします。②申請→承認フローの整理を、判断基準と決裁権限の階層（No.32）とセットでプロセス改革の検討項目に追加します。上長間の優先順位確認は月例の案件会議で行います。フロー設計への参画をお願いします。</t>
         </is>
       </c>
     </row>

--- a/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
+++ b/docs/sales-reform-toolkit/フィードバック回答_新谷コメント.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>採用します。STO専任化は「現任業務の引き継ぎ計画」とセットでなければ現場に穴が空きます。その前提として、まず現在STO候補となるメンバーに依頼している業務・サポート中の案件が何かを正確に把握したいので、現状の依頼内容の一覧共有をお願いします。そのうえで人選確定時には、選定基準と担当案件の移管先・スケジュールを必ずセットで提示し承認します。移管が成立しなければ専任化の時期をずらします。</t>
+          <t>重要な論点だと認識しています。STOの人選・体制はまだ確定しておらず、現任業務への影響をどう防ぐかは体制を決める際の前提として扱います。その把握のため、現在STO候補となるメンバーに依頼している業務・サポート中の案件の一覧を共有いただけると助かります。</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>AIが担うのは提案書の初稿までで、企画クリエイティブは当面「人」が担います。ここがボトルネックという認識は同じです。そこで庄司さんにお願いがあります。①現状の提案書作成のワークフローを共有してください。②提案資料の「基本資料パック」（標準で使い回している共通資料）があれば共有してください。③もし案件ごとにオートクチュール（一点もの）で資料を作っているのであれば、その作成にかかっている時間の把握にご協力ください。この実態を踏まえて、デザインリソースの強化（No.20と接続）をデータを根拠に判断します。</t>
+          <t>現時点で確定した方針はありませんが、AIに任せられる範囲と人が担う範囲の線引きは、設計の中心論点だと考えています。検討の材料として、①現状の提案書作成の流れ、②標準で使い回している共通資料の有無、③案件ごとに個別制作している場合の作成時間感——を教えてください。</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>同意します。改革の定義に「作品・メディアディストリビューションとの連動」を明記する修正を行います。監修改革WGとスコアリング基準の設計に、TFEIからの参画をご相談します。</t>
+          <t>同意します。作品・メディアディストリビューションを改革の定義・範囲にどう位置づけるかは、設計時の重要論点として扱います。その際はTFEIのご意見を伺わせてください。</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2点とも設計に反映します。監修の定義は「品質保証＋提案機能」と明記し、AIは過去指摘の検索と一次チェックまで、判断と提案は人が担う分担にします。AIに蓄積したナレッジを現場教育に使う仕組みもWGの要件に加えます。監修の優先順位付けは3トラック制の設計時に監修部門と決めます。</t>
+          <t>2点とも重要な論点です。監修は品質保証だけでなく提案機能を持つという認識、AI化が進むほど当事者意識が薄れるリスク——いずれも監修まわりを設計する際に必ず扱います。その際は監修部門・TFEIと一緒に検討させてください。</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>採用します。契約・監修・ローンチ・レベニューシェア特定まで同一IDで一気通貫管理することを、プロセス改革WGの設計要件に明記します。</t>
+          <t>同意します。採番制による一気通貫の管理は有力な選択肢として、プロセス設計の検討材料にします。具体的な仕組みはこれから設計します。</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>「決め方の設計」の話という整理はその通りです。撤退より省力化を優先する／判断基準に再参入可能性を織り込む／別れ方の標準（誠実な説明・代替提案・再開可能性）をセットにする——の3点で設計します。トリアージ基準の設計に、ぜひ参画をお願いしたい。</t>
+          <t>「決め方の設計」の話という整理はその通りだと思います。IP特有の「やめると戻れなくなる」リスクをどう判断に織り込むかは、まだ答えを持っていません。基準を設計する段階で、橋本さんの経験を前提に議論させてください。</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>採用します。データ基盤要件に追加し、標準化フェーズ（4〜6か月目）で単一基盤化します。棚卸しの際に各部門の既存カレンダー・管理表も洗い出します。</t>
+          <t>課題認識は同じです。全社横断のカレンダー・情報基盤は検討テーマとして扱います。まずは各部門が現状どんな管理表を使っているかの把握から始めたいと考えています。</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>採用します。獲得で終わらず相手のビジネスの成功に並走し続けるのが当社営業の特色というご指摘はその通りで、標準プロセスを「リード→商談→提案→条件合意→契約→監修→プロモーション→立ち上げ・運用→フォローアップ」に修正します。発売後フォロー・販売支援の工数も計測対象に含め、見えない貢献が評価されない状態をなくします。次の商品化提案は「別案件として起票」で認識合っています（同一顧客に紐づくので、関係の継続性は顧客側で管理されます）。</t>
+          <t>ご指摘はその通りだと思います。発売後のフォローアップ・販売支援まで含めてプロセスをどう定義するかは、標準プロセスを設計する際の論点に含めます。「次の商品化提案は別案件か」という点も含め、設計の際に成岡さんと確認させてください。</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>重要な指摘で、2点とも対応します。①分単位の正確な記憶は求めません。0.5時間単位・記憶ベース・精度7割で十分という設計です（正確さより続くことを優先）。そのうえで、音声メモを入れると要約・分類して記録化してくれるAI支援は、まさに構想している「商談記録の自動化」ユースケースそのものなので、AI試験導入の候補に正式に加えます。トライアル希望の営業管理ツールの件も含めて検討します。②活動工程の10分類は全社共通の「粗い物差し」として設計していますが、部門特有の工程があるのはその通りなので、領域ごとの追加項目を認める設計にします。連携窓口役を通じて各部門の実情に合わせて調整しましょう。</t>
+          <t>2点とも大事な指摘です。時間の記録は「正確さより続けられること」を優先する考えですが、具体的な入力方法・分類・AI支援の要否はまだ決めていません。部門による工程の違いも含め、設計の際に現場の実情を聞かせてください。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>同意します。7つの評価軸（CRM価値・ブランド価値・海外展開価値・戦略価値）は、まさにライブのような「単年度売上に表れない価値」を正当に評価するために設計しています。継続開催によるLTVの観点は顧客ランクとスコア運用に反映します。工数についても重要なご指摘で、工数分類に「品質維持・ブランド価値向上のための投資工数」（スーツメンテ・キャスト育成等）の区分を設け、削減対象と混ざらないようにします。工数計測は削るためだけでなく「必要な投資を証明するため」にも使ってください。</t>
+          <t>同意します。ライブ事業を単年度収益だけで評価しないこと、品質維持のための工数を削減対象と区別すること——いずれも評価軸・工数分類を設計する際の論点として扱います。その際は田中さんに前提を確認させてください。</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>同意します。浸透のために、メンバー向け説明会（15分＋想定問答）を全領域で実施し、決定事項は台帳で全員に見える形にします。属人化の顕在化はまさに第1段階の棚卸しの目的です。「あの人しか知らない」を責めるのではなく、組織の資産に変換する趣旨で進めますので、流通営業部での説明会にはぜひ田代さんにも同席いただきたいです。</t>
+          <t>同意します。全社への浸透のやり方、属人化の顕在化の進め方は、これから具体化します。流通営業部の実情を伺いながら進めさせてください。</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>同意します。毀損リスク案件は点数に関わらずエスカレーションする設計とし、ウェイトを決める経営検討会でこのご意見を正式議題にします。加えて、この機会にやりたいのは「ブランド毀損とは何か」の形式知化です。毀損にあたる条件は何か、ウルトラマンのイメージに合うパートナー・プロジェクトとはどういうものか——これまで暗黙知で判断されてきた基準を明文化し、誰が見ても同じ判断ができる状態にします。この基準づくりに田代さんの知見をぜひお借りしたい。</t>
+          <t>同意します。ブランドバリューへの寄与を判断の中心に置くべきという考えは同じです。現状は「毀損とは何か・組みたい相手とは何か」を判断できる明文化された基準がないことが課題なので、基準づくりを検討テーマとして扱います。その際は田代さんの知見をお借りしたい。</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>同意します。これまでトップ外交が成果につながってこなかったのは事実なので、登録→アサイン→30日以内初動のルールに変えます。記録・追跡は事務局が持ち、案件化の判断時には担当部門の工数・実現性を確認するステップを入れます。現場との乖離を感じたら月次会議で指摘してください。</t>
+          <t>同意します。トップ外交がこれまで十分に成果につながってこなかったという現状認識も同じです。現場との乖離（負荷・コスト・モチベーション）を生まないことは、仕組みを設計する際の必須条件として扱います。</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>採用します。ファンベース拡大への取組と「未開拓地域への協力」を取引先評価に加える——顧客ランクの「海外価値」軸は『未開拓市場の扉を開ける力』を評価する設計にしており、国内の未開拓地域・チャネルへの貢献も同じ思想で織り込みます。そして「定性的な項目には基準がほしい」はその通りです。すでに5段階の点数それぞれに『具体的な状態』を紐づけた採点定義（誰が採点しても同じ点になるアンカー方式）を作成済みで、近日展開します。『こんなすごいところとやれる』という実績が持つシグナル効果（ブランドの格を上げる協業）も、ブランド軸の採点定義に含めます。測り方の細部は、ウェイトを決める経営検討会の前に成岡さんの知見を聞かせてください。</t>
+          <t>趣旨、受け取りました。ファンベース拡大や未開拓地域への貢献をどう評価に入れるか、定性的な項目の基準をどう作るかは、評価軸を設計する際の論点です。測り方について、成岡さんの考えを設計の前に聞かせてください。</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>採用します。第1段階に「社内システム・保存先の棚卸し」を追加し、6か月目のシステム投資判断の前提にします。AI試験導入2件は既存システムへの依存が小さいため、整理と並行で進めます。</t>
+          <t>課題認識は同じです。システムと保存先の乱立は、AI活用以前の問題としてどこかで整理が必要だと考えています。進め方はこれから検討します。</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>その通りだと思います。仕組みとしては、評価に使わない・停滞表示は支援のシグナル・明細は本人と事務局のみ、を徹底します。実際に運用が始まったら、ネガティブな報告が不利に扱われていないか、永山さんの目でも見ていてください。おかしければ直します。</t>
+          <t>その通りだと思います。管理強化にしないこと、ネガティブな情報を出せる運用にすることは、設計全体の前提条件として扱います。運用が始まった後、おかしいと感じる点があれば指摘してください。</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>同意します。やらない判断は経営の名前で出し、決定台帳で見える化します。ご指摘を受け、「決定事項のかみ砕き版（1決定1段落）」を事務局から毎月出す運用を加えます。ただし、これを1社員まで届け切る最後の区間は、部長の皆さんの部内展開なしには実現できません。かみ砕き版は事務局が用意しますので、部内へ届ける役はぜひお願いします。</t>
+          <t>同意します。「良心で続いている仕事」をどう扱うか、決定事項を1社員まで届ける方法は、運用を設計する際の論点に含めます。周知の仕方は部長の皆さんとも相談させてください。</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>その機能を担うのが専任推進チーム（事務局）です。各部門のタスクとスケジュールの振り出し・進捗管理を役割として明確に持たせ、各部門には連携窓口役を置いて受け口も明確にします。</t>
+          <t>リードする機能が必要だという認識は同じです。それをどこが担うか（事務局の役割・権限の範囲）は、体制設計の中で決めます。</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>採用します。売上・利益・在庫の週次ダッシュボードは第2段階で優先度高く設計し、担当者レベルの週次レビューは自社MD領域から先行導入しましょう。</t>
+          <t>方向性に同意します。自社MDの収支・在庫の見える化と担当者レベルのレビューは、見える化を設計する際の論点として受け取りました。具体的な形は永山さんと相談しながら決めたいです。</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>重要な提案として持ち帰ります。営業改革の直接範囲は超えますが、No.2の課題（提案書の企画イメージ作成）とナレッジ基盤に直結するため、「経営基盤強化」の検討テーマとして正式に起票します。</t>
+          <t>重要な提案として受け取りました。デザイン組織の強化とアート資産の管理・蓄積は営業改革の直接範囲を超えますが、関連する論点（No.2・24など）と合わせて扱い方を検討します。</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>同意します。経営のコミットは、月次会議への出席・撤退判断・48時間ルールの実行で担保します。コア人員は専任化と現業の移管計画をセットで確定し、「推進する担当」と「現状業務を守る担当」は分けます。人員が減っている中での改革だという前提は体制設計に織り込みますので、リソース計画は高橋さんと詰めさせてください。</t>
+          <t>同意します。コア人員のリソース確保と、現業への影響をどう防ぐかは、体制設計の最重要論点です。「推進する側と現状業務を守る側の明確化」というご提案も含め、具体的な体制はこれから設計するので、高橋さんと相談させてください。</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>大変ありがたいお申し出です。契約改革WG（雛形整備・条件標準メニュー・過去契約の検索可能化・採番制）を先行して立ち上げます。HD側人材のアサインについて、今週中に個別にご相談させてください。</t>
+          <t>ありがたいお申し出です。契約まわりは優先度高く着手したい領域なので、進め方とHD側人材の件を高橋さんと個別に相談させてください。</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>現場が疲弊しているという認識は私も同じです。そのうえで、進め方は次の通りにします。①現場へのお願いより先に、資料作成の廃止・リスト下書きの巻き取りなど、負荷が減るものから着手する。②処遇への反映は、現時点で安易に約束はしません。評価制度との接続は改革後半で正式に設計し、その時点で方針を示します。③全社への発信は、毎月の決定事項の共有と節目ごとのメッセージで続けます。部長の皆さんの日々の声掛けと併せてお願いします。</t>
+          <t>現場が疲弊しているという認識は私も同じです。負荷のかけ方の順序と発信の仕方は、進め方を設計するうえで最も気をつける点として受け取りました。処遇への反映は現時点で約束できませんが、論点として持ち続けます。全社への発信は継続します。</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>採用します。AIが担うのは提案書の初稿までで、クリエイティブ制作はデザイナーの支援が必要——庄司さん（No.2）・永山さん（No.20）と同根の論点です。まず工数計測で販売促進部への依頼の実態（件数・工数・繁閑）を把握し、それを根拠に販促部のリソース強化・体制整備を検討スコープに含めます。実態把握の際はご協力ください。</t>
+          <t>ご指摘の通り、AIで対応しきれない場面でのデザイナー支援は論点です。販促部の受け入れ余力も含めて、まず実態の把握から始めたいと考えているので、その際はご協力ください。リソース強化をスコープに含めるかどうかは、実態を見たうえで判断します。</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>重要な指摘です。会長直下の案件も含めて、面談・案件は48時間以内の登録→担当アサイン→30日以内初動のルールに乗せます。例外は作りません。会長が出席する点検会議で進捗を確認する運用にすることで、個人に紐づいた情報が組織で共有される状態にします。</t>
+          <t>重要な指摘です。会長直下案件の情報が個人に紐づき、組織の取り組みにならないという構造は、この改革で扱うべき課題として受け取りました。どう仕組みに乗せるかは設計時に検討します。</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>同意します。負荷が一部に集中していないかは工数データで確認し、会議で再配分を判断します。また、品質・安全が不十分な状態で世に出すことは成果とみなさない前提で運営します。スピードと品質のバランスが崩れていると感じたら、その時点で指摘してください。</t>
+          <t>同意します。スピードを優先するあまり一部に負荷が集中し、品質・安心安全が損なわれるリスクは、運営を設計するうえでの前提として扱います。バランスが崩れていると感じたら、その時点で指摘してください。</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>同意します。仕組みの側も同じ考え方で運営します。90日ごとに仕組み自体を見直し、機能していないものは廃止・変更します。運用が前例踏襲になっていると気づいたら、都度指摘してください。</t>
+          <t>同意します。仕組みの側も、作って終わりにせず見直し続ける前提で設計します。</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>採用します。作品・企画情報が営業現場まで届かず、個別説明の手間が双方に発生しているのはロスです。対応として、①全社マーケティングカレンダー（No.7で採用済み）に製作企画のタイムラインを統合、②案件一覧の基盤に作品・企画情報のビューを追加、③標準プロセスの上流に企画段階からの営業・製作の対話ステップを設計——を進めます。この設計に製作企画部の参画をお願いします。</t>
+          <t>課題認識は同じです。作品・企画情報と営業の間の情報流通は、双方にロスが出ている重要な論点として受け取りました。どう仕組み化するかは、製作企画部と一緒に設計させてください。</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>重要なテーマとして受け取りました。IP開発への投資判断は営業改革の直接範囲を超えますが、「作品単体の収支シミュレーションを基盤に、ブランド軸・グループ貢献軸を含めた判断基準を作る」という方向は、案件の7軸評価と完全に同じ思想です。投資開発判断基準の共同設計に賛成します。HDとの原資・成長投資枠の議論は経営アジェンダとして正式に起票します。まず現状の作品単体収支シミュレーションの仕組みを教えてください。そこを出発点にしましょう。</t>
+          <t>重要なテーマとして受け取りました。IP開発投資の判断基準づくりは営業改革の直接範囲を超えますが、評価の考え方には通じるものがあるので、扱い方を検討します。まず現状の作品単体収支シミュレーションの仕組みを教えてください。</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>スコープの認識、合っています（商品開発本部・カード開発部も対象です）。そして「行動設計＋予算＋評価の三点セット」というご指摘は本質です。そのうえで順序の設計意図をお伝えします。予算との連携は、6か月目のシステム投資判断と来期予算へのKPI組み込みで対応します。評価制度との連携は、意図的に改革後半（10〜12か月目）に置いています——初年度前半に評価と結びつけると「工数記録＝査定」という誤解が生まれ、データが歪むためです。横連携を促す評価設計は定着化フェーズで必ず扱いますので、その際は宍戸さんの知見をお借りしたい。</t>
+          <t>スコープの認識は合っています（商品開発本部・カード開発部も対象です）。予算・評価制度との連携が必要というご指摘は本質だと思います。どの順序で扱うかも含めて設計の論点にします。特に評価との接続は慎重に順序を考えたいので、その際は宍戸さんと相談させてください。</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>賛成です。カードアプリのユーザーデータは、全社の顧客データ基盤の先行事例になります。データは分析が目的ではなく課題発見・仮説検証のため、という前提も同じ認識です。領域別のKPI設計（売上/収録カード数、ユーザーの獲得・維持・復帰・成長など）はカード領域から着手しましょう。データポータルを拝見したうえで、設計の時間をください。</t>
+          <t>賛成です。カードアプリのデータと「データは課題発見・仮説検証のため」という考え方は、全社の設計の参考になります。領域別の指標のアイデアも、ぜひ個別に聞かせてください。データポータルも拝見します。</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>重要な指摘で、採用します。見える化の目的は経営が全部を握ることではなく、現場で決め切れる範囲を広げることです。運営原則も「現場で決められることは現場で決め切る。上の会議にはそこでしか決められないことだけを上げる」としています。ご提案の判断権限の3階層基準（経営判断／部門長判断／担当者が自走できる範囲）は明文化し、決裁基準表として標準プロセスに組み込みます。経営基盤強化の検討テーマに追加します。</t>
+          <t>重要な指摘で、認識は同じです。見える化の目的は経営が全部を握ることではなく、現場で決められる範囲を明確にすることだと考えています。ご提案の判断権限の階層基準（経営判断／部門長判断／担当者の自走範囲）は、設計時の論点として扱います。</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>同意します。「どんなブランドと組んでいきたいか」は、進行中の「ブランド毀損基準の形式知化」（No.12）の裏面です。毀損条件のネガティブリストだけでなく、「目指す協業像・組みたい相手」のポジティブリストもセットで明文化します。PR・ブランディング・クリエイティブ開発との連携強化は、案件評価のIP適合軸の運用に組み込みます。この基準づくりに、HD側の視点でぜひ参画してください。</t>
+          <t>同意します。「どんなブランドと組みたいか」の明文化された基準がないことは課題だと思います。基準づくりを検討する際は、HD側の視点でぜひ参画してください。</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>面白いご提案です。そして内覧会でいただいたストリート系ファッションブランドからの声は、まさに「接点から生まれた商談の種」です。仕組みの実践第1号として、さっそく案件登録→担当アサイン→30日以内の初動につなげましょう（詳細を教えてください）。ウルトラマートの営業拠点としての活用は、接点づくりの検討テーマとして正式に起票します。</t>
+          <t>面白い話をありがとうございます。ファッションブランドの件は機会を逃したくないので、詳細を教えてください。ウルトラマートの営業拠点としての活用も、検討する価値のあるテーマとして受け取りました。</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>同意します。新しい顧客層を取りに行くには、デザイン・世界観・PR/SNSの一貫性が生命線というご指摘はその通りです。クリエイティブ組織の強化は永山さん（No.20）・井上さん（No.24）と同根のテーマとして「経営基盤強化」に正式起票済みで、木綿さんのご意見もそこに束ねます。加えて「リサーチ強化」（グループインタビュー・ターゲット理解・商品開発のアイデア出し）は新しい論点で、消費者・ファン理解＝接点づくりの検討テーマに組み込みます。HD側の視点で、ぜひ設計に参画してください。</t>
+          <t>同意します。クリエイティブ面の組織強化とリサーチ（ターゲット理解）の強化は、関連する複数のご指摘（No.20・24など）と合わせて扱い方を検討します。</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>同意します。企画・キャンペーン設計・クリエイティブを自分たちから仕掛けられる体制は、営業を許諾の受け窓口で終わらせないために必要です。この論点は庄司さん（No.2）・永山さん（No.20）・井上さん（No.24）・No.35と束ねて、企画・クリエイティブ体制の強化として一つの検討テーマで扱います。第1号案件として、No.34のファッションブランドの件を具体化しましょう。</t>
+          <t>同意します。企画・キャンペーン設計・クリエイティブを自分たちから仕掛けられる体制という論点は、関連するご指摘と束ねて検討します。</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>重要な論点です。キャラクター稼働・連動企画の依頼がライブイベント部に集中し、申請ベースで受け続けている構造は、見える化と優先順位づけの対象そのものです。対応は2つ。①部門横断の依頼も「案件」として登録し、工数と優先順位が全社で見える状態にする——依頼側の熱量ではなく共通の物差しで判断できるようにします。②申請→承認フローの整理を、判断基準と決裁権限の階層（No.32）とセットでプロセス改革の検討項目に追加します。上長間の優先順位確認は月例の案件会議で行います。フロー設計への参画をお願いします。</t>
+          <t>重要な論点です。キャラクター稼働・連動企画の依頼がライブイベント部に集中し、申請ベースで受け続けている構造は、優先順位の決め方とフローの整理が必要な課題として受け取りました。整理の仕方は、菅野さんと関係部門の上長を交えて検討させてください。</t>
         </is>
       </c>
     </row>
